--- a/data/trans_camb/P2C_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 21,0</t>
+          <t>1,49; 21,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,66; 11,2</t>
+          <t>-13,18; 11,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-61,49; -40,18</t>
+          <t>-62,38; -40,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,84; 27,57</t>
+          <t>6,63; 27,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 22,32</t>
+          <t>0,65; 22,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-55,71; -32,77</t>
+          <t>-55,71; -33,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,69; 21,49</t>
+          <t>5,8; 20,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 13,62</t>
+          <t>-3,24; 12,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-55,91; -40,82</t>
+          <t>-55,96; -40,47</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 30,5</t>
+          <t>2,07; 32,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,88; 15,5</t>
+          <t>-16,39; 16,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-76,69; -56,92</t>
+          <t>-76,92; -57,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,45; 44,15</t>
+          <t>8,63; 44,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,03; 35,38</t>
+          <t>0,95; 36,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-72,76; -49,69</t>
+          <t>-72,95; -50,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,7; 31,89</t>
+          <t>7,29; 29,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 19,39</t>
+          <t>-4,3; 18,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-72,32; -58,47</t>
+          <t>-71,99; -57,64</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,71; 30,61</t>
+          <t>9,77; 30,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 11,32</t>
+          <t>-11,12; 12,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-54,4; -31,58</t>
+          <t>-52,61; -29,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,2; 29,56</t>
+          <t>12,34; 30,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 9,61</t>
+          <t>-12,69; 8,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-59,59; -36,71</t>
+          <t>-59,58; -36,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,71; 27,14</t>
+          <t>14,34; 26,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 6,69</t>
+          <t>-9,88; 7,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-54,14; -36,99</t>
+          <t>-54,18; -36,38</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>13,86; 47,04</t>
+          <t>11,89; 45,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,49; 17,19</t>
+          <t>-14,12; 19,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-68,63; -45,31</t>
+          <t>-67,97; -42,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,35; 43,57</t>
+          <t>14,76; 44,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,43; 13,94</t>
+          <t>-15,86; 12,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-73,84; -51,88</t>
+          <t>-73,34; -50,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,11; 39,28</t>
+          <t>18,17; 39,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 9,28</t>
+          <t>-12,38; 10,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-68,61; -51,66</t>
+          <t>-68,86; -51,29</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,02; 40,35</t>
+          <t>16,73; 40,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 24,99</t>
+          <t>-4,02; 25,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-41,75; -10,84</t>
+          <t>-42,7; -11,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,75; 28,04</t>
+          <t>7,2; 29,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 14,89</t>
+          <t>-10,22; 14,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-48,19; -22,15</t>
+          <t>-47,36; -21,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,24; 30,15</t>
+          <t>13,38; 30,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 14,83</t>
+          <t>-4,04; 14,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-41,33; -21,8</t>
+          <t>-42,21; -22,5</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,67; 81,33</t>
+          <t>24,29; 81,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 47,97</t>
+          <t>-6,05; 47,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-62,69; -18,82</t>
+          <t>-65,09; -21,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,36; 46,35</t>
+          <t>9,73; 49,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-14,47; 23,93</t>
+          <t>-13,98; 24,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-67,93; -33,7</t>
+          <t>-66,84; -34,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,15; 50,77</t>
+          <t>19,19; 52,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 25,81</t>
+          <t>-5,83; 25,3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-61,74; -36,53</t>
+          <t>-62,96; -36,29</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,23; 30,44</t>
+          <t>15,47; 30,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,83; 17,1</t>
+          <t>0,8; 17,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-51,98; -31,3</t>
+          <t>-51,92; -31,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,29; 25,39</t>
+          <t>10,25; 25,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 15,93</t>
+          <t>-0,04; 16,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-47,3; -30,82</t>
+          <t>-48,64; -31,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,32; 25,3</t>
+          <t>15,15; 26,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,6; 14,29</t>
+          <t>2,52; 14,82</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-47,16; -33,92</t>
+          <t>-48,12; -34,68</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>21,99; 50,79</t>
+          <t>21,5; 49,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,62; 27,91</t>
+          <t>1,1; 28,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-74,71; -49,41</t>
+          <t>-75,77; -51,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14,35; 40,48</t>
+          <t>13,77; 40,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 25,6</t>
+          <t>-0,16; 25,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-66,07; -47,04</t>
+          <t>-67,28; -47,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,28; 39,88</t>
+          <t>21,2; 41,12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,75; 22,68</t>
+          <t>3,49; 23,39</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-68,23; -52,37</t>
+          <t>-70,04; -53,37</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,47; 28,04</t>
+          <t>7,79; 27,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 15,86</t>
+          <t>-5,41; 16,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-49,92; -27,4</t>
+          <t>-49,18; -26,73</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,37; 33,01</t>
+          <t>14,65; 33,03</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 20,12</t>
+          <t>-1,91; 20,08</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-39,52; -11,3</t>
+          <t>-38,98; -12,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,4; 27,79</t>
+          <t>14,45; 28,11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 14,59</t>
+          <t>0,27; 15,58</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-40,28; -22,38</t>
+          <t>-40,7; -23,12</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>9,77; 44,43</t>
+          <t>9,82; 43,17</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 24,64</t>
+          <t>-6,96; 25,65</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-64,39; -41,65</t>
+          <t>-63,87; -41,03</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19,13; 53,15</t>
+          <t>19,26; 54,07</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 32,47</t>
+          <t>-2,45; 31,86</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-53,77; -16,92</t>
+          <t>-53,44; -19,5</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,11; 42,15</t>
+          <t>19,39; 43,82</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 21,98</t>
+          <t>0,74; 23,9</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-54,45; -32,71</t>
+          <t>-54,31; -32,89</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>9,99; 30,4</t>
+          <t>9,27; 30,46</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-25,1; 2,42</t>
+          <t>-25,06; 1,43</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-43,39; -16,95</t>
+          <t>-43,88; -17,11</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5,33; 28,48</t>
+          <t>4,51; 28,58</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 18,1</t>
+          <t>-6,96; 19,83</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-26,7; 0,66</t>
+          <t>-27,84; 0,18</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,5; 26,57</t>
+          <t>9,04; 26,0</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-11,77; 6,51</t>
+          <t>-12,21; 7,12</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-30,97; -11,38</t>
+          <t>-31,43; -11,19</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>13,36; 48,88</t>
+          <t>12,28; 49,15</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-33,02; 4,34</t>
+          <t>-33,36; 2,17</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-58,64; -25,77</t>
+          <t>-58,54; -26,32</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7,58; 53,16</t>
+          <t>7,23; 52,42</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 33,0</t>
+          <t>-9,97; 36,98</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-40,69; 0,93</t>
+          <t>-41,31; 0,2</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13,29; 43,49</t>
+          <t>12,76; 43,06</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-16,89; 10,78</t>
+          <t>-17,63; 11,74</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-44,46; -18,99</t>
+          <t>-45,09; -17,9</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>15,84; 24,35</t>
+          <t>16,15; 24,33</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 8,49</t>
+          <t>-1,33; 8,23</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-45,7; -34,73</t>
+          <t>-45,09; -35,3</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14,99; 22,95</t>
+          <t>14,97; 23,18</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,22; 11,09</t>
+          <t>2,05; 11,21</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-41,08; -30,91</t>
+          <t>-41,2; -31,25</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,88; 22,44</t>
+          <t>16,86; 22,35</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,82; 8,15</t>
+          <t>2,02; 8,29</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-41,34; -33,89</t>
+          <t>-41,61; -34,46</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>21,97; 36,9</t>
+          <t>22,42; 36,64</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 12,64</t>
+          <t>-1,8; 12,44</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-64,33; -51,49</t>
+          <t>-63,11; -51,52</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>20,71; 34,31</t>
+          <t>20,89; 35,11</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>3,08; 16,71</t>
+          <t>2,94; 16,94</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-57,57; -45,75</t>
+          <t>-57,5; -45,99</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,83; 33,57</t>
+          <t>23,92; 33,3</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2,64; 12,13</t>
+          <t>2,87; 12,17</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-59,24; -50,2</t>
+          <t>-58,88; -50,46</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 21,73</t>
+          <t>1,3; 22,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 11,66</t>
+          <t>-13,84; 11,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-62,38; -40,64</t>
+          <t>-61,59; -41,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,63; 27,77</t>
+          <t>6,03; 27,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 22,94</t>
+          <t>0,35; 21,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-55,71; -33,34</t>
+          <t>-55,91; -33,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,8; 20,78</t>
+          <t>6,71; 21,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 12,79</t>
+          <t>-2,81; 13,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-55,96; -40,47</t>
+          <t>-56,14; -40,55</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,07; 32,22</t>
+          <t>1,64; 32,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,39; 16,35</t>
+          <t>-17,53; 15,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-76,92; -57,16</t>
+          <t>-76,57; -57,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,63; 44,19</t>
+          <t>8,02; 42,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 36,18</t>
+          <t>0,47; 33,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-72,95; -50,07</t>
+          <t>-73,26; -50,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,29; 29,75</t>
+          <t>8,42; 32,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 18,42</t>
+          <t>-3,57; 18,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-71,99; -57,64</t>
+          <t>-72,28; -57,89</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,77; 30,04</t>
+          <t>9,92; 29,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,12; 12,96</t>
+          <t>-11,84; 11,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-52,61; -29,32</t>
+          <t>-53,9; -31,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,34; 30,22</t>
+          <t>11,34; 29,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 8,85</t>
+          <t>-14,18; 9,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-59,58; -36,79</t>
+          <t>-59,94; -37,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,34; 26,83</t>
+          <t>14,26; 28,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,88; 7,48</t>
+          <t>-9,3; 7,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-54,18; -36,38</t>
+          <t>-52,97; -36,82</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,89; 45,78</t>
+          <t>12,39; 45,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,12; 19,47</t>
+          <t>-14,88; 17,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-67,97; -42,85</t>
+          <t>-68,84; -44,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,76; 44,64</t>
+          <t>13,68; 42,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 12,65</t>
+          <t>-17,32; 12,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-73,34; -50,73</t>
+          <t>-73,16; -50,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,17; 39,03</t>
+          <t>17,84; 41,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 10,53</t>
+          <t>-11,71; 10,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-68,86; -51,29</t>
+          <t>-68,08; -51,97</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>16,73; 40,6</t>
+          <t>15,06; 39,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 25,21</t>
+          <t>-6,66; 23,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-42,7; -11,78</t>
+          <t>-41,35; -10,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,2; 29,33</t>
+          <t>6,46; 28,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,22; 14,81</t>
+          <t>-10,28; 15,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-47,36; -21,3</t>
+          <t>-48,62; -20,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,38; 30,12</t>
+          <t>13,7; 30,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 14,81</t>
+          <t>-3,28; 15,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-42,21; -22,5</t>
+          <t>-41,4; -21,07</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24,29; 81,24</t>
+          <t>21,52; 76,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 47,5</t>
+          <t>-9,7; 45,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-65,09; -21,61</t>
+          <t>-63,88; -19,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,73; 49,17</t>
+          <t>8,85; 48,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 24,14</t>
+          <t>-14,23; 25,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-66,84; -34,19</t>
+          <t>-68,42; -33,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,19; 52,01</t>
+          <t>19,8; 51,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 25,3</t>
+          <t>-4,96; 25,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-62,96; -36,29</t>
+          <t>-61,43; -35,28</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,47; 30,25</t>
+          <t>14,95; 29,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,8; 17,25</t>
+          <t>0,88; 17,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-51,92; -31,86</t>
+          <t>-51,84; -32,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,25; 25,32</t>
+          <t>10,89; 25,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 16,5</t>
+          <t>-0,9; 15,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-48,64; -31,41</t>
+          <t>-47,93; -31,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,15; 26,04</t>
+          <t>14,74; 25,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,52; 14,82</t>
+          <t>3,18; 14,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-48,12; -34,68</t>
+          <t>-47,19; -33,75</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>21,5; 49,68</t>
+          <t>20,85; 49,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,1; 28,34</t>
+          <t>1,03; 28,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-75,77; -51,15</t>
+          <t>-75,52; -51,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,77; 40,02</t>
+          <t>15,24; 41,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 25,99</t>
+          <t>-1,14; 24,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-67,28; -47,9</t>
+          <t>-66,53; -48,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,2; 41,12</t>
+          <t>20,91; 40,51</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,49; 23,39</t>
+          <t>4,44; 22,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-70,04; -53,37</t>
+          <t>-68,6; -52,8</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,79; 27,6</t>
+          <t>7,97; 27,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 16,49</t>
+          <t>-4,17; 17,26</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-49,18; -26,73</t>
+          <t>-49,15; -25,64</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,65; 33,03</t>
+          <t>14,63; 32,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 20,08</t>
+          <t>-1,78; 19,65</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-38,98; -12,61</t>
+          <t>-39,97; -13,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,45; 28,11</t>
+          <t>14,42; 28,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,27; 15,58</t>
+          <t>0,12; 15,6</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-40,7; -23,12</t>
+          <t>-40,67; -22,17</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>9,82; 43,17</t>
+          <t>10,17; 43,11</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 25,65</t>
+          <t>-5,77; 26,06</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-63,87; -41,03</t>
+          <t>-63,41; -39,52</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19,26; 54,07</t>
+          <t>19,53; 53,85</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 31,86</t>
+          <t>-2,33; 31,15</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-53,44; -19,5</t>
+          <t>-53,99; -19,61</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,39; 43,82</t>
+          <t>19,3; 43,63</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0,74; 23,9</t>
+          <t>0,2; 24,06</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-54,31; -32,89</t>
+          <t>-54,94; -33,03</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>9,27; 30,46</t>
+          <t>9,66; 31,31</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-25,06; 1,43</t>
+          <t>-24,3; 1,84</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-43,88; -17,11</t>
+          <t>-43,08; -15,39</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4,51; 28,58</t>
+          <t>4,69; 28,86</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 19,83</t>
+          <t>-8,24; 18,05</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-27,84; 0,18</t>
+          <t>-26,75; 1,81</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,04; 26,0</t>
+          <t>9,81; 26,18</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-12,21; 7,12</t>
+          <t>-11,3; 6,72</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-31,43; -11,19</t>
+          <t>-31,45; -12,33</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>12,28; 49,15</t>
+          <t>12,8; 50,12</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-33,36; 2,17</t>
+          <t>-32,33; 2,56</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-58,54; -26,32</t>
+          <t>-57,75; -23,77</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7,23; 52,42</t>
+          <t>7,28; 53,54</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-9,97; 36,98</t>
+          <t>-11,93; 33,36</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-41,31; 0,2</t>
+          <t>-40,79; 3,47</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>12,76; 43,06</t>
+          <t>14,19; 43,58</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-17,63; 11,74</t>
+          <t>-16,83; 10,85</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-45,09; -17,9</t>
+          <t>-45,36; -19,73</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>16,15; 24,33</t>
+          <t>16,67; 24,33</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 8,23</t>
+          <t>-1,15; 8,06</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-45,09; -35,3</t>
+          <t>-45,56; -34,95</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14,97; 23,18</t>
+          <t>14,91; 23,14</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,05; 11,21</t>
+          <t>1,79; 11,0</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-41,2; -31,25</t>
+          <t>-40,58; -30,79</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,86; 22,35</t>
+          <t>17,06; 22,45</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2,02; 8,29</t>
+          <t>2,2; 8,51</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-41,61; -34,46</t>
+          <t>-41,1; -33,94</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>22,42; 36,64</t>
+          <t>23,25; 36,73</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 12,44</t>
+          <t>-1,59; 12,11</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-63,11; -51,52</t>
+          <t>-63,76; -51,82</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>20,89; 35,11</t>
+          <t>20,95; 35,11</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,94; 16,94</t>
+          <t>2,49; 16,51</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-57,5; -45,99</t>
+          <t>-57,52; -45,65</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,92; 33,3</t>
+          <t>24,04; 33,3</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>2,87; 12,17</t>
+          <t>3,07; 12,56</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-58,88; -50,46</t>
+          <t>-58,62; -50,2</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2C_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2C_R-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>16,39</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11,06</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-42,65</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>11,53</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-0,92</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-52,26</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>16,39</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,06</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-44,79</t>
+          <t>-51,86</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-48,5</t>
+          <t>-47,21</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 22,03</t>
+          <t>5,84; 27,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,84; 11,16</t>
+          <t>0,1; 22,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-61,59; -41,19</t>
+          <t>-53,52; -30,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,03; 27,18</t>
+          <t>0,86; 21,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 21,43</t>
+          <t>-13,66; 11,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-55,91; -33,08</t>
+          <t>-61,27; -39,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,71; 21,91</t>
+          <t>6,69; 21,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 13,28</t>
+          <t>-3,23; 13,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-56,14; -40,55</t>
+          <t>-54,56; -39,45</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>22,95%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15,49%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-59,72%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>15,1%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-1,2%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-68,47%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>22,95%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>15,49%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-62,72%</t>
+          <t>-67,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-65,52%</t>
+          <t>-63,79%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 32,4</t>
+          <t>7,45; 44,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-17,53; 15,78</t>
+          <t>0,03; 35,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-76,57; -57,23</t>
+          <t>-70,36; -47,68</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,02; 42,92</t>
+          <t>1,21; 30,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 33,84</t>
+          <t>-16,88; 15,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-73,26; -50,01</t>
+          <t>-76,48; -56,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,42; 32,04</t>
+          <t>8,7; 31,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 18,82</t>
+          <t>-3,99; 19,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-72,28; -57,89</t>
+          <t>-70,73; -56,24</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>20,5</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-2,09</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-47,88</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>20,27</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,04</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-42,49</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>20,5</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-2,09</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-48,48</t>
+          <t>-41,77</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-45,48</t>
+          <t>-44,77</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,92; 29,81</t>
+          <t>11,2; 29,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,84; 11,41</t>
+          <t>-12,86; 9,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-53,9; -31,03</t>
+          <t>-58,77; -35,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,34; 29,05</t>
+          <t>10,71; 30,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 9,16</t>
+          <t>-11,47; 11,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-59,94; -37,68</t>
+          <t>-53,75; -30,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,26; 28,05</t>
+          <t>13,71; 27,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 7,15</t>
+          <t>-10,17; 6,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-52,97; -36,82</t>
+          <t>-53,53; -36,13</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>26,78%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-2,73%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-62,54%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>27,52%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-0,05%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-57,68%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>26,78%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-2,73%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-63,33%</t>
+          <t>-56,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-60,56%</t>
+          <t>-59,62%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,39; 45,68</t>
+          <t>13,35; 43,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-14,88; 17,11</t>
+          <t>-15,43; 13,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-68,84; -44,94</t>
+          <t>-73,29; -50,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,68; 42,8</t>
+          <t>13,86; 47,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-17,32; 12,8</t>
+          <t>-14,49; 17,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-73,16; -50,94</t>
+          <t>-68,42; -44,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,84; 41,22</t>
+          <t>17,11; 39,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,71; 10,5</t>
+          <t>-12,64; 9,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-68,08; -51,97</t>
+          <t>-68,04; -50,51</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>17,7</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,36</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-35,08</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>28,21</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>9,48</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-27,07</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>17,7</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,36</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-35,43</t>
+          <t>-25,77</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-31,94</t>
+          <t>-31,06</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,06; 39,24</t>
+          <t>5,75; 28,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 23,75</t>
+          <t>-10,33; 14,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-41,35; -10,57</t>
+          <t>-48,25; -21,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,46; 28,74</t>
+          <t>16,02; 40,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 15,69</t>
+          <t>-6,39; 24,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-48,62; -20,93</t>
+          <t>-40,54; -9,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,7; 30,17</t>
+          <t>14,24; 30,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 15,25</t>
+          <t>-4,76; 14,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-41,4; -21,07</t>
+          <t>-40,54; -20,86</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>26,4%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-52,34%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>46,64%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>15,68%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-44,76%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>26,4%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-52,86%</t>
+          <t>-42,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-49,63%</t>
+          <t>-48,27%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>21,52; 76,6</t>
+          <t>8,36; 46,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 45,49</t>
+          <t>-14,47; 23,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-63,88; -19,52</t>
+          <t>-67,98; -33,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,85; 48,37</t>
+          <t>23,67; 81,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-14,23; 25,71</t>
+          <t>-9,3; 47,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-68,42; -33,66</t>
+          <t>-61,23; -14,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,8; 51,11</t>
+          <t>21,15; 50,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 25,92</t>
+          <t>-6,93; 25,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-61,43; -35,28</t>
+          <t>-60,35; -34,24</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>17,98</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7,95</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-39,68</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>23,07</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>9,07</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-41,17</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>17,98</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7,95</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-39,89</t>
+          <t>-39,49</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-40,52</t>
+          <t>-39,5</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,95; 29,78</t>
+          <t>10,29; 25,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,88; 17,54</t>
+          <t>-0,31; 15,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-51,84; -32,0</t>
+          <t>-47,21; -30,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,89; 25,51</t>
+          <t>15,23; 30,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 15,46</t>
+          <t>1,83; 17,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-47,93; -31,03</t>
+          <t>-47,32; -30,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,74; 25,77</t>
+          <t>14,32; 25,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,18; 14,52</t>
+          <t>2,6; 14,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-47,19; -33,75</t>
+          <t>-45,36; -33,36</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>26,21%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>11,59%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-57,86%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>34,92%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>13,73%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-62,32%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>26,21%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>11,59%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-58,16%</t>
+          <t>-59,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-60,2%</t>
+          <t>-58,69%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>20,85; 49,05</t>
+          <t>14,35; 40,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,03; 28,25</t>
+          <t>-0,37; 25,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-75,52; -51,03</t>
+          <t>-65,95; -46,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,24; 41,02</t>
+          <t>21,99; 50,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 24,55</t>
+          <t>2,62; 27,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-66,53; -48,56</t>
+          <t>-67,69; -48,84</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,91; 40,51</t>
+          <t>20,28; 39,88</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,44; 22,5</t>
+          <t>3,75; 22,68</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-68,6; -52,8</t>
+          <t>-64,8; -51,42</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>23,92</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>9,89</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-27,4</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>17,72</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>5,28</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-38,62</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>23,92</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>9,89</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-27,89</t>
+          <t>-36,94</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-32,52</t>
+          <t>-31,66</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,97; 27,47</t>
+          <t>14,37; 33,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 17,26</t>
+          <t>-0,78; 20,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-49,15; -25,64</t>
+          <t>-39,33; -12,14</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,63; 32,81</t>
+          <t>7,47; 28,04</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 19,65</t>
+          <t>-5,22; 15,86</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-39,97; -13,61</t>
+          <t>-48,13; -25,31</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,42; 28,12</t>
+          <t>14,4; 27,79</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,12; 15,6</t>
+          <t>-0,13; 14,59</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-40,67; -22,17</t>
+          <t>-38,99; -21,79</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>34,65%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>14,32%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-39,69%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>24,54%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>7,31%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-53,48%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>34,65%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>14,32%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-40,41%</t>
+          <t>-51,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-46,15%</t>
+          <t>-44,93%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>10,17; 43,11</t>
+          <t>19,13; 53,15</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 26,06</t>
+          <t>-1,04; 32,47</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-63,41; -39,52</t>
+          <t>-52,92; -18,04</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19,53; 53,85</t>
+          <t>9,77; 44,43</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 31,15</t>
+          <t>-6,62; 24,64</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-53,99; -19,61</t>
+          <t>-61,9; -38,42</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,3; 43,63</t>
+          <t>19,11; 42,15</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0,2; 24,06</t>
+          <t>-0,21; 21,98</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-54,94; -33,03</t>
+          <t>-53,3; -32,83</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>17,46</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>6,07</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-10,88</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>20,26</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-11,42</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-30,55</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>17,46</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>6,07</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-13,52</t>
+          <t>-32,1</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-22,02</t>
+          <t>-21,66</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>9,66; 31,31</t>
+          <t>5,33; 28,48</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-24,3; 1,84</t>
+          <t>-6,3; 18,1</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-43,08; -15,39</t>
+          <t>-24,47; 3,57</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4,69; 28,86</t>
+          <t>9,99; 30,4</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 18,05</t>
+          <t>-25,1; 2,42</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-26,75; 1,81</t>
+          <t>-45,21; -18,22</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,81; 26,18</t>
+          <t>9,5; 26,57</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-11,3; 6,72</t>
+          <t>-11,77; 6,51</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-31,45; -12,33</t>
+          <t>-30,61; -10,91</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>28,4%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>9,87%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-17,7%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>28,65%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-16,15%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-43,19%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>28,4%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>9,87%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-21,99%</t>
+          <t>-45,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-33,28%</t>
+          <t>-32,73%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>12,8; 50,12</t>
+          <t>7,58; 53,16</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-32,33; 2,56</t>
+          <t>-9,72; 33,0</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-57,75; -23,77</t>
+          <t>-37,21; 6,01</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7,28; 53,54</t>
+          <t>13,36; 48,88</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-11,93; 33,36</t>
+          <t>-33,02; 4,34</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-40,79; 3,47</t>
+          <t>-60,94; -28,62</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14,19; 43,58</t>
+          <t>13,29; 43,49</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-16,83; 10,85</t>
+          <t>-16,89; 10,78</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-45,36; -19,73</t>
+          <t>-44,53; -18,31</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>19,04</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>6,76</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-34,85</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>20,29</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>3,44</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-40,12</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>19,04</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>6,76</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-35,8</t>
+          <t>-38,86</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-37,84</t>
+          <t>-36,76</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>16,67; 24,33</t>
+          <t>14,99; 22,95</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 8,06</t>
+          <t>2,22; 11,09</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-45,56; -34,95</t>
+          <t>-40,06; -29,89</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14,91; 23,14</t>
+          <t>15,84; 24,35</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,79; 11,0</t>
+          <t>-1,05; 8,49</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-40,58; -30,79</t>
+          <t>-43,41; -34,16</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,06; 22,45</t>
+          <t>16,88; 22,44</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2,2; 8,51</t>
+          <t>1,82; 8,15</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-41,1; -33,94</t>
+          <t>-39,93; -33,0</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>27,67%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>9,82%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-50,63%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>29,14%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>4,94%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-57,62%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>27,67%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>9,82%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-52,01%</t>
+          <t>-55,81%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-54,66%</t>
+          <t>-53,11%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>23,25; 36,73</t>
+          <t>20,71; 34,31</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 12,11</t>
+          <t>3,08; 16,71</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-63,76; -51,82</t>
+          <t>-56,49; -44,57</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>20,95; 35,11</t>
+          <t>21,97; 36,9</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,49; 16,51</t>
+          <t>-1,49; 12,64</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-57,52; -45,65</t>
+          <t>-60,56; -50,41</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,04; 33,3</t>
+          <t>23,83; 33,57</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>3,07; 12,56</t>
+          <t>2,64; 12,13</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-58,62; -50,2</t>
+          <t>-57,21; -48,85</t>
         </is>
       </c>
     </row>
